--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_o_higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:44</t>
+    <t xml:space="preserve">2026-09-24 01:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -964,16 +964,16 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>-0.4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.07</v>
@@ -987,19 +987,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="21">
@@ -1010,16 +1010,16 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.24</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.15</v>
@@ -1033,16 +1033,16 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.41</v>
@@ -1079,19 +1079,19 @@
         <v>34</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.41</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.34</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="25">
@@ -1102,19 +1102,19 @@
         <v>34</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="26">
@@ -1125,19 +1125,19 @@
         <v>34</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.03</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.36</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="27">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_o_higgins.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:33</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_o_higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
